--- a/Pharmacologie special/data/Medicaments.xlsx
+++ b/Pharmacologie special/data/Medicaments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Pharmacologie special\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B41232-86A1-40C1-9FE7-F3922F522083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB1DD2E-E999-4427-8946-54A6C8F174C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{23BBE10C-2248-48DB-9954-FA348B838493}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5483" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5489" uniqueCount="1103">
   <si>
     <t>Nom du médicament</t>
   </si>
@@ -3327,6 +3327,24 @@
   </si>
   <si>
     <t>Classe_médicament_2</t>
+  </si>
+  <si>
+    <t>Méthylphénidate</t>
+  </si>
+  <si>
+    <t>Lisdexamfétamine</t>
+  </si>
+  <si>
+    <t>Guanfacine</t>
+  </si>
+  <si>
+    <t>Modafinil</t>
+  </si>
+  <si>
+    <t>Pitolisant</t>
+  </si>
+  <si>
+    <t>Oxybate</t>
   </si>
 </sst>
 </file>
@@ -11797,6 +11815,9 @@
       <c r="B189" s="1" t="s">
         <v>562</v>
       </c>
+      <c r="C189" t="s">
+        <v>1097</v>
+      </c>
       <c r="D189" s="1" t="s">
         <v>562</v>
       </c>
@@ -11865,6 +11886,9 @@
       <c r="B190" s="1" t="s">
         <v>562</v>
       </c>
+      <c r="C190" t="s">
+        <v>1098</v>
+      </c>
       <c r="D190" s="1" t="s">
         <v>562</v>
       </c>
@@ -11933,6 +11957,9 @@
       <c r="B191" s="1" t="s">
         <v>562</v>
       </c>
+      <c r="C191" t="s">
+        <v>1099</v>
+      </c>
       <c r="D191" s="1" t="s">
         <v>562</v>
       </c>
@@ -11980,6 +12007,9 @@
       <c r="B192" s="1" t="s">
         <v>562</v>
       </c>
+      <c r="C192" t="s">
+        <v>1100</v>
+      </c>
       <c r="D192" s="1" t="s">
         <v>562</v>
       </c>
@@ -12021,6 +12051,9 @@
       <c r="B193" s="1" t="s">
         <v>562</v>
       </c>
+      <c r="C193" t="s">
+        <v>1101</v>
+      </c>
       <c r="D193" s="1" t="s">
         <v>562</v>
       </c>
@@ -12061,6 +12094,9 @@
       </c>
       <c r="B194" s="1" t="s">
         <v>562</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1102</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>562</v>
